--- a/daily_matches/job_matches_2026-05-29.xlsx
+++ b/daily_matches/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Federal Home Loan Bank of Pittsburgh</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, PostgreSQL, MongoDB</t>
+          <t>Data Scientist, RAG, Gemini, S3, Redshift, BigQuery, Data Lake, Kinesis, Apache Airflow, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706e45c82f6dc417</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5878406660b75c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - AI Agents</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Westmont, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, NoSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a981c9a05200e9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7074c3f94f41b012</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Senior Software Engineer - AI Agents</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059e365e3de8e316</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca74eb2bd1e115e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee533d88723392eb</t>
+          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Centreville, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38fd78df3d590a31</t>
+          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Architect / Data Engineer - 26-06256</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19599523bbd9a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Consultant, Generative AI</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SIA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, Docker, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84ad4dea871c5572</t>
+          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Consultant, Generative AI</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SIA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, Docker, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e74f8d335acb66</t>
+          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RCN Capital, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Windsor, CT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, NoSQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25277a0adce5e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Intern Agentic AI Developer (Summer 2026)</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, Docker, Git, Python</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b81f0b90411494c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9e36ab343f5c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, GitHub Actions, Git, Dask, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ddac6595638098</t>
+          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Automation Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Cortex, Git, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e951e309584aa9a</t>
+          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer, Fleet Analytics, Cell Quality &amp; Field Reliability</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, MySQL, MongoDB, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c653f5b18c837aab</t>
+          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30c5e927e6d68165</t>
+          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d25c9c531d22c59</t>
+          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a48a8a96330b451</t>
+          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DTAI (Data-Tech-AI) Intern</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a6711b96bec62f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Junior Data Scientist</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Applied Research Associates, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, Git, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59fca8e98f5bfaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9197d59dd49c11ba</t>
+          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 – Data Integration / ETL / Analytics - 26-06253</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cedar Park, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cortex, GitHub Actions, Git, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5606661108e2367d</t>
+          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 – Data Integration / ETL / Analytics - 26-06253</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cortex, GitHub Actions, Git, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5605e56ce3fac78</t>
+          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 – Data Integration / ETL / Analytics - 26-06253</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cortex, GitHub Actions, Git, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,1967 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85ba3ff0ceff890d</t>
+          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Systems Analyst 3 – Data Integration / ETL / Analytics - 26-06253</t>
+          <t>Senior AI Engineer - SFL Scientific</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Georgetown, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TD</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI-Accelerated Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5277afe7a27c982</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sr Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Thousand Oaks, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Databricks</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Philip Morris International</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Apache Airflow, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI &amp; Analytics Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Trident Maritime Systems</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, TensorFlow, Docker, Kubernetes, CI/CD, Git, Databricks, Kafka, Power BI</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5962b832b4441ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Cloud Engineer - Project Delivery Specialist</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4571a774e0ddfe2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NIKE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Beaverton, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Glue, Athena, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bf48fdb6d5d10f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Associate AI Engineer (Entry Level)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Astute Business Solutions</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, FastAPI, Git, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c714ffcca32b78d</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, CI/CD, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f104122b969993ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Engineer, IT Data</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Development Engineer - Factory Automation</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>South Portland, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Azure Databrick Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Jasvik Solutions</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Azure ML, BigQuery, Synapse, Data Lake, Databricks, BigQuery, PySpark, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaf7dd433be6641f</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Azure Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MCAConnect</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Git, Databricks, NoSQL, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a58a6d64105b0558</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff16b9b763785e37</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Enterprise Applications Developer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Gemini, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecda10d7c9f6fa22</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Enterprise Applications Developer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Gemini, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c363c6383022c0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Generative AI</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d405557724645e50</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NIKE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Beaverton, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Glue, CI/CD, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c71425b3f2507123</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior AI DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Equinix</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, S3, Redshift, BigQuery, Docker, Git, BigQuery, Redshift</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42d90ce61776c34b</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI and Data Science Engineer (TS/SCI Poly)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38dbad16f86725f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Shaw Industries</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dalton, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Dataflow, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Salesforce Technical AI Engineer (Delivery Management Engineer III)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Databricks, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a06fac2f6cce9ed8</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Vehicle Order Fulfillment</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e974b04295119a48</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Enterprise AI &amp; Automation Analyst</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>St. Petersburg College</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Prompt Engineering, Data Lake, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f812f1d587b911e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NIKE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Beaverton, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Glue, Data Lake, CI/CD, Jenkins, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software quality engineer (US)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1334289f6f0d8ab8</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software quality engineer (US)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6f65e850dbc5aa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Software quality engineer (US)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Writer</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b57f2b57f71c34c</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>iManage</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Azure ML, Data Lake, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Full stack Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Abbott Park, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e85ee4c9b9accfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
         <v>10</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Cortex, GitHub Actions, Git, Snowflake, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4c3cc0a6deb508c</t>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Kubernetes, Kafka, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be987a0dea512025</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbb9d403ea3dd281</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Software Engineer Sys 2 (Gen AI)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Lam Research</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Generative AI, FAISS, Prompt Engineering, Docker, Kubernetes, CI/CD, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e051dcab18e411c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Analytics and Research Analyst</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56f2cd13ea0096bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>UL Solutions</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Northbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Data Scientist, PyTorch, CI/CD, Git, Power BI, Matplotlib, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a0b8245c4c84a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Junior Engineer - AI Process Optimization</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Docuware</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Beacon, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Git, MongoDB, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bc7354f0b48fb2e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-29.xlsx
+++ b/daily_matches/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,77 +486,77 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Gemini, S3, Redshift, BigQuery, Data Lake, Kinesis, Apache Airflow, Terraform</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5878406660b75c</t>
+          <t>https://www.indeed.com/viewjob?jk=b251bad156120ee9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Agents</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7074c3f94f41b012</t>
+          <t>https://www.indeed.com/viewjob?jk=825e221841f6b0ce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI Agents</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>Data Scientist, RAG, Copilot, Redshift, Synapse, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca74eb2bd1e115e</t>
+          <t>https://www.indeed.com/viewjob?jk=bad92e6915049edc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, Glue, Athena, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25de7d2183b60020</t>
+          <t>https://www.indeed.com/viewjob?jk=30f59e2bfb4a8152</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bayer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,392 +626,392 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Keras, BigQuery, CI/CD, Git, BigQuery, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5254b51487c541bf</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4227fa5413fb6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>RAG, FAISS, Pinecone, S3, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e1c9f851e59ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=3701c804c9b0b189</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Engineer (Agent Systems)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Faraday Future</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>RAG, FAISS, Pinecone, S3, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296cd63f5dbbf7dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5592fc9e666f0b6d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, S3, FastAPI, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad8b9ab8938d109</t>
+          <t>https://www.indeed.com/viewjob?jk=6bc40683645d5866</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Software Engineer - AI Engineer II/III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f647aebc05097c6d</t>
+          <t>https://www.indeed.com/viewjob?jk=597fd01ae92b355a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Redshift, Docker, Kubernetes, AKS, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfce4aabc870c1e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0a0dc2930f694</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>AI Engineering Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Redshift, Docker, Kubernetes, AKS, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ac08cb6fc28f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2790efc31f46d191</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Business Technology Solutions Consultant R&amp;D</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Redshift, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94350957d9c97848</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea69dc22803ae1d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Git, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ca2c5b809b3e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=567500816bcb880f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Senior Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Git, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05c2f8241dbc3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=33bf0b6d5ba97700</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Prompt Engineering, Databricks, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7670a327cdbace2b</t>
+          <t>https://www.indeed.com/viewjob?jk=16c48102f3cbafa7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Senior - MLOps/LLMOps Engineer, Development</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,1117 +1021,1117 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c79929a16fab26b</t>
+          <t>https://www.indeed.com/viewjob?jk=796c1b2eafcb17e6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Synapse, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034adb3237511f83</t>
+          <t>https://www.indeed.com/viewjob?jk=1558bff9d1119b05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Sr Data Scientist I - (AI Focus)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Principal Financial Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Keras, AWS SageMaker, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3068d43e0a8784f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f17cc52ed3b6538</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, CI/CD, Git, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445b422fbba7c0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=fc3130fd4a42b451</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Generative AI, RAG, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73ff3c6e80deb66b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd8dc23d0848aec</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Advanced Data Science Associate Consultant - Generative AI and Machine Learning</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>South San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d16e2ee9f0a09204</t>
+          <t>https://www.indeed.com/viewjob?jk=7f5173c77dae3157</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Forward Deployed Data Scientist Expert</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Git, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41e7eb598184fa6b</t>
+          <t>https://www.indeed.com/viewjob?jk=24ad6c719b38e2d2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2a217b517b6b24</t>
+          <t>https://www.indeed.com/viewjob?jk=43479a5e279bea94</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abca0c73f0ae4f32</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9dce1dbceabf77</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Site AI Engineer - New Haven, CT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Haven, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8abd2bdf3e5e9d65</t>
+          <t>https://www.indeed.com/viewjob?jk=d29adf993445f0bd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Site AI Engineer - Boston, MA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d4be44614b53d9</t>
+          <t>https://www.indeed.com/viewjob?jk=bcf91e3de3b3cfaa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Site AI Engineer - Temple, TX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0fff2e56e03c1</t>
+          <t>https://www.indeed.com/viewjob?jk=02502cf23954a80e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Site AI Engineer - Las Vegas, NV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0966280767501eae</t>
+          <t>https://www.indeed.com/viewjob?jk=71a6429c12809608</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Site AI Engineer - Dallas, TX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0c19305c77e755d</t>
+          <t>https://www.indeed.com/viewjob?jk=94942178e7603ad0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Site AI Engineer - Fort Meyers, FL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5c9b6498d7725b</t>
+          <t>https://www.indeed.com/viewjob?jk=1119ddab775a5553</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ARCO a Family of Construction Companies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fead9b33e4a9d978</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a09d1dcbe620e2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ARCO a Family of Construction Companies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79977c8ace4ee985</t>
+          <t>https://www.indeed.com/viewjob?jk=f543ff315b33da9c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ARCO a Family of Construction Companies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f2ea212d574734</t>
+          <t>https://www.indeed.com/viewjob?jk=049d3a549641cd8d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ARCO a Family of Construction Companies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad73be87ce8b9d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1402163d11ec92a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Site AI Engineer - USVI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e55d828dba7c070</t>
+          <t>https://www.indeed.com/viewjob?jk=d2dcedc535de31f7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>DevOps &amp; Cloud Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=956b9fa32c7e89f9</t>
+          <t>https://www.indeed.com/viewjob?jk=3794df2d185fe68c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Perfect Path, LLC, d/b/a Trajector Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, S3, Kubernetes, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2011206cf0e10b63</t>
+          <t>https://www.indeed.com/viewjob?jk=21a0bf48b6619f48</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AARP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Generative AI, Gemini, TensorFlow, PyTorch, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf0bea965250073f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb820560aeb2034b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Engineer - SFL Scientific</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1026585ae9f2eef0</t>
+          <t>https://www.indeed.com/viewjob?jk=2099233b2412293a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Scientist II (AI/ML - Fraud/Risk, GenAI &amp; Agentic AI)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, MLflow, CI/CD</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0a170c085d1afe</t>
+          <t>https://www.indeed.com/viewjob?jk=09edda39b98ef300</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI-Accelerated Full Stack Software Development Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5277afe7a27c982</t>
+          <t>https://www.indeed.com/viewjob?jk=b96821caf0970503</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Sr. Software Development Engineer - Orchestration Platform, Temporal, Fleet Management (Flexibility on level)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Docker, Kubernetes, AKS</t>
+          <t>RAG, Data Lake, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f5e1ae2551595</t>
+          <t>https://www.indeed.com/viewjob?jk=45cb78b6b93f4548</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Databricks</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d531875d9bfd27</t>
+          <t>https://www.indeed.com/viewjob?jk=24937a6185650d43</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Power BI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>Foot Locker</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, AWS SageMaker, Apache Airflow, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, PostgreSQL, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3592d349c9e3bdd7</t>
+          <t>https://www.indeed.com/viewjob?jk=20e67e817b932fdd</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI &amp; Analytics Solutions Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trident Maritime Systems</t>
+          <t>HealthEdge</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, Docker, Kubernetes, CI/CD, Git, Databricks, Kafka, Power BI</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5962b832b4441ae</t>
+          <t>https://www.indeed.com/viewjob?jk=80f2d4cc8d5ebe0f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Engineer - Project Delivery Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Perfect Path, LLC, d/b/a Trajector Services</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, CI/CD, GitHub Actions, Git, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adab2c82b9dd303f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e3500830c844d2d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Digital Enterprise DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arnold AFB, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4571a774e0ddfe2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9f43023d7db0b07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Mobile Developer - Ecommerce</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, Copilot, CI/CD, PostgreSQL, MongoDB, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf48fdb6d5d10f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c756eff2cfb314f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Systems Engineer – Cloud Platform &amp; Automation</t>
+          <t>Shopify E-Commerce Architect Remote</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>Generative AI, RAG, S3, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,207 +2176,207 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1373c97d41f96938</t>
+          <t>https://www.indeed.com/viewjob?jk=650a2db40b4383ec</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate AI Engineer (Entry Level)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Astute Business Solutions</t>
+          <t>Ohio State University Physicians</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, FastAPI, Git, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, AKS, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c714ffcca32b78d</t>
+          <t>https://www.indeed.com/viewjob?jk=4879b2098b6d2202</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ohio State University Physicians</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, CI/CD, Kafka, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, AKS, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f104122b969993ef</t>
+          <t>https://www.indeed.com/viewjob?jk=260a0da01516723d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Frontwave Credit Union</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, Redshift, Snowflake, Redshift, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5bf627e3fe34512</t>
+          <t>https://www.indeed.com/viewjob?jk=488da3ead0efe4c0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Factory Automation</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Sabre Systems</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>South Portland, ME, US USA</t>
+          <t>Lexington Park, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Git, Matplotlib, Seaborn, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=063db503e4975e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4461df92815c90d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Databrick Engineer</t>
+          <t>Senior AI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jasvik Solutions</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure ML, BigQuery, Synapse, Data Lake, Databricks, BigQuery, PySpark, Power BI, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf7dd433be6641f</t>
+          <t>https://www.indeed.com/viewjob?jk=2fe42af2e3734689</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure Senior Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MCAConnect</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Git, Databricks, NoSQL, Power BI, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,102 +2386,102 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58a6d64105b0558</t>
+          <t>https://www.indeed.com/viewjob?jk=856be8aae55eebf3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cybersecurity Senior Engineer – Cloud Security</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Prompt Engineering, FastAPI, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff16b9b763785e37</t>
+          <t>https://www.indeed.com/viewjob?jk=d6dbd21e206b6b5e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Joby Aviation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Prompt Engineering, FastAPI, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a2e22fa42d1c49</t>
+          <t>https://www.indeed.com/viewjob?jk=6c7bd32285a09685</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer</t>
+          <t>Senior Engineer 2, Inventory Visibility</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gemini, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Pinecone, Prompt Engineering, CI/CD, Kafka, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,277 +2491,277 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecda10d7c9f6fa22</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b8afed22b2107a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Enterprise Applications Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>BlackLine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gemini, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c363c6383022c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=22b7d0d557e5c8f6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Generative AI</t>
+          <t>AI Automation Developer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Yale New Haven Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Stratford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d405557724645e50</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4f3e15b0e54b1c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Glue, CI/CD, Databricks, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c71425b3f2507123</t>
+          <t>https://www.indeed.com/viewjob?jk=62c0fef2bf9474cc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer</t>
+          <t>Senior Cloud Architect - Hybrid</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Highmark Residential</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lebanon, NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, S3, Redshift, BigQuery, Docker, Git, BigQuery, Redshift</t>
+          <t>Data Lake, CI/CD, Terraform, Git, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42d90ce61776c34b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c457677f3b1d3e6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI and Data Science Engineer (TS/SCI Poly)</t>
+          <t>Senior Power Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Git, Power BI, R, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38dbad16f86725f9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f348caf77484474</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Industrial IT/OT Integration Specialist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shaw Industries</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dalton, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Dataflow, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Data Lake, Git, Kafka, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af744cc881ed105f</t>
+          <t>https://www.indeed.com/viewjob?jk=74d230c5ab0229a0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Salesforce Technical AI Engineer (Delivery Management Engineer III)</t>
+          <t>Engineering Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Databricks, R</t>
+          <t>RAG, Cortex, S3, Glue, Snowflake, Databricks, PySpark, R, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06fac2f6cce9ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=35e60c72e365c000</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Vehicle Order Fulfillment</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,137 +2771,137 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e974b04295119a48</t>
+          <t>https://www.indeed.com/viewjob?jk=41989306f0664062</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise AI &amp; Automation Analyst</t>
+          <t>Senior Data Scientist Consultant (Python, SQL, TensorFlow, PyTorch, Scikit-Learn, FTE, Onsite)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>St. Petersburg College</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Prompt Engineering, Data Lake, Git, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, scikit-learn, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f812f1d587b911e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f68feadfc4fbb65b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Healthcare Data Analyst or Senior Data Analyst, Analytics Hub</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>ECG Management Consultants</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Glue, Data Lake, CI/CD, Jenkins, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0689c9e8b937d497</t>
+          <t>https://www.indeed.com/viewjob?jk=e6270fae3f533dbf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software quality engineer (US)</t>
+          <t>AI Intern – Co-op Fall 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Exact Sciences</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1334289f6f0d8ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=6682f71d115f31de</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software quality engineer (US)</t>
+          <t>Security Specialist - Akamai Security Suite Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+          <t>RAG, CI/CD, Terraform, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f65e850dbc5aa9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e46c68109a11c2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software quality engineer (US)</t>
+          <t>Senior Fullstack Engineer - ecommerce platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>Labviva</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,287 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b57f2b57f71c34c</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>iManage</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RAG, Azure ML, Data Lake, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=417d720e6c2b1b27</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Full stack Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Abbott</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Abbott Park, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e85ee4c9b9accfe</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>DocuSign</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Kubernetes, Kafka, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be987a0dea512025</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>DocuSign</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb9d403ea3dd281</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Software Engineer Sys 2 (Gen AI)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Lam Research</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Generative AI, FAISS, Prompt Engineering, Docker, Kubernetes, CI/CD, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e051dcab18e411c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56f2cd13ea0096bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>UL Solutions</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Northbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Data Scientist, PyTorch, CI/CD, Git, Power BI, Matplotlib, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0b8245c4c84a7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Junior Engineer - AI Process Optimization</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Docuware</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Beacon, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Git, MongoDB, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc7354f0b48fb2e</t>
+          <t>https://www.indeed.com/viewjob?jk=bbb7fbda10aef21d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-29.xlsx
+++ b/daily_matches/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data &amp; AI Intern</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Key Prediction</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, LLaMA, Gemini, Mistral, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, Docker, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5586ae9539a9ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9832efe0efb1942</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Azure ML, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, FastAPI, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88dfb056c5c3b9b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Auctane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be471e01eea2f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b98655cee0687224</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Software Engineer III - Big Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Sightview Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kubernetes, Redshift, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb8f91201caafc33</t>
+          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>SunnyData</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>RAG, S3, Kubernetes, Terraform, Databricks, Kafka, Hadoop, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a68b9b44071451</t>
+          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Platform Engineer (Google Cloud Platform)</t>
+          <t>Forward Deployed Data Engineer Expert</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, BigQuery, Docker, CI/CD, Terraform, BigQuery</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, CI/CD, Git, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d8a92dff07ca15</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Full Stack Engineer</t>
+          <t>Cloud Engineer - DevOps</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hiro Talent Solutions</t>
+          <t>Innovative Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Tableau, Power BI</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c770b1c4f512c431</t>
+          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Mimecast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, Git, Snowflake, Kafka, NoSQL</t>
+          <t>RAG, Copilot, S3, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c48c04bec794a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect - Remote</t>
+          <t>Forward Deployed Data Scientist Expert</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Azure ML, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Git, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c32603ea351f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fd2bca70b00b83</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Agent Builder</t>
+          <t>Forward Deployed Data Scientist Expert</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Next Level Now, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Beverly, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, MySQL, MongoDB, Cassandra, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Git, Databricks, PySpark, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e4190c349e88ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5d5c7f6ae9c7f0ac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital Markets Gateway</t>
+          <t>Open Lending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Peru, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a337926ac08cbc6</t>
+          <t>https://www.indeed.com/viewjob?jk=02227c456a2f4e76</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Development Engineer (SDE3/4) - Evergreen</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital Markets Gateway</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>London, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31127bd14c34fc23</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd4ecad9dda4445</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital Markets Gateway</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>London, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8aa3958c702c053</t>
+          <t>https://www.indeed.com/viewjob?jk=ba63b4dd3048a815</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Git, Python, SQL, R, Scala, Optimization, Bayesian</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc69c48979debfd</t>
+          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Cloud Applications New</t>
+          <t>Software Engineer: On-board Autonomy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Temporal Technologies</t>
+          <t>Lodestar Space</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Kinesis, Kubernetes, Redshift, Kafka, PostgreSQL, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0c42ad13150702</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a367ffbddb5511</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Infrastructure &amp; Reliability Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DAT Solutions</t>
+          <t>KWI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Git, PostgreSQL, MySQL, SQL, R, Scala, Optimization</t>
+          <t>Copilot, Docker, CI/CD, Terraform, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4412e8d5e4b1a5ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9e7d78bb2b6867e4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. AI Forward Deployment Engineer</t>
+          <t>Senior Application Security Engineer / AppSec Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, CI/CD, Databricks, Python, R, Java, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e564bb9027464bed</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8e7995889e5f42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEPT OF PARKS &amp; RECREATION</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,182 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43a37629446d48f0</t>
+          <t>https://www.indeed.com/viewjob?jk=14aa8e7defd55832</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hardware DevOps/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Intel Corporation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Folsom, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96995b95c2729cf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer: Perception</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lodestar Space</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, OpenCV, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b38f437f2ab2fb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ensemble Health Partners</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Blue Ash, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Terraform, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b5fb0039f7b3d74</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Irvington, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Digital Product Analytics</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GPS Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eef0f56ce7e465fd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-29.xlsx
+++ b/daily_matches/job_matches_2026-05-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data &amp; AI Intern</t>
+          <t>AI Engineer/Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, Docker, CI/CD, Jenkins</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Prompt Engineering, S3, Redshift, Synapse, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9832efe0efb1942</t>
+          <t>https://www.indeed.com/viewjob?jk=7604b89af99ba406</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>Baanyan Software Services, Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, FastAPI, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f326fc2210a7954</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ebc389447ab4ae</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Auctane</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL</t>
+          <t>RAG, S3, EC2, Data Lake, Docker, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b98655cee0687224</t>
+          <t>https://www.indeed.com/viewjob?jk=0761c7021676d118</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sightview Software</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kubernetes, Redshift, PySpark, NoSQL</t>
+          <t>Data Scientist, RAG, S3, Data Lake, Docker, CI/CD, Terraform, Git, PySpark, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102fc288fbb9abdd</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7c12478eb19af9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Solutions Architect - Platform, Cloud Infrastructure and Security</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SunnyData</t>
+          <t>Echo Global Logistics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, Terraform, Databricks, Kafka, Hadoop, Cassandra, NoSQL, Python</t>
+          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Data Lake, Git, Redshift, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47aa02c81d1c7a60</t>
+          <t>https://www.indeed.com/viewjob?jk=eae8bcb49c9597d5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer Expert</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, CI/CD, Git, Databricks, PySpark, Kafka, Python</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Databricks, PySpark, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1f104bd0b18db7</t>
+          <t>https://www.indeed.com/viewjob?jk=17cb9776bd0e7f4a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer - DevOps</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Innovative Solutions</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ed8a47e56a014</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2bfc17d54981e1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Product Foundations</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, SQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736f22eed6fef2</t>
+          <t>https://www.indeed.com/viewjob?jk=0277abc185dfb7c6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Scientist Expert</t>
+          <t>SMTS/LMTS Full Stack Software Engineer, Tableau Next</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Git, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Data Lake, Snowflake, Databricks, NoSQL, Tableau, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fd2bca70b00b83</t>
+          <t>https://www.indeed.com/viewjob?jk=a68a382a207b6b3d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Scientist Expert</t>
+          <t>Senior BI Analyst - IGEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Git, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>Copilot, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d5c7f6ae9c7f0ac</t>
+          <t>https://www.indeed.com/viewjob?jk=acd6baf60c6afe77</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer - IGEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Open Lending</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Appleton, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Snowflake, Kafka, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02227c456a2f4e76</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0ca36351ff88fb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Development Engineer (SDE3/4) - Evergreen</t>
+          <t>GTM Engineer - ABM, Advertising and Growth Marketing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd4ecad9dda4445</t>
+          <t>https://www.indeed.com/viewjob?jk=2b02041a59d83dfb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, Snowflake, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba63b4dd3048a815</t>
+          <t>https://www.indeed.com/viewjob?jk=3ce519e36124f5ab</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Software Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Castlight</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, Snowflake, BigQuery, MySQL, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89dd9964d8bd40d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5023cf7cd4ba777</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer: On-board Autonomy</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lodestar Space</t>
+          <t>BlueCross BlueShield of Tennessee</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Azure ML, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a367ffbddb5511</t>
+          <t>https://www.indeed.com/viewjob?jk=7bd124012dcd3482</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Reliability Engineer</t>
+          <t>Senior Data Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KWI</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Melville, NY, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Terraform, Git, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Jenkins, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e7d78bb2b6867e4</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd4faeed9a50a59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer / AppSec Architect</t>
+          <t>Machine Learning Engineer - Generative AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8e7995889e5f42</t>
+          <t>https://www.indeed.com/viewjob?jk=9ed04e0d49a37c50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior DevOps Engineer - AWS (Perm, USA, Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>nearForm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14aa8e7defd55832</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cc6dbf61526b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hardware DevOps/AI Engineer</t>
+          <t>Senior DevOps Engineer - AWS (Perm, USA, Remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>nearForm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96995b95c2729cf1</t>
+          <t>https://www.indeed.com/viewjob?jk=342b3074a26d6e8e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer: Perception</t>
+          <t>Software Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lodestar Space</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, OpenCV, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>Prompt Engineering, Glue, Docker, CI/CD, Git, PostgreSQL, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b38f437f2ab2fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa6f25bbf69ef3d9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer</t>
+          <t>Software Engineer, Agentic AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Prompt Engineering, Glue, Docker, CI/CD, Git, PostgreSQL, MySQL, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5fb0039f7b3d74</t>
+          <t>https://www.indeed.com/viewjob?jk=b125fbdb1276b8d1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, MLflow, Databricks, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,462 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a189ac16e1f72f61</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffee8cb623137f9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist, Digital Product Analytics</t>
+          <t>.Net Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>WhiztekCorp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99ae3f832b40aeec</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III-SI&amp;DS Design</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Newark, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5517f2fb4f43af4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Enrichment &amp; Content Intelligence</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, BigQuery, Dataflow, BigQuery, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3380efa07021533b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Elastic Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Freddie Mac</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eef0f56ce7e465fd</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1786b88ef9132db</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Infoblox</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tacoma, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7f39b1373683285</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Platform DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PVcase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5a4c402a7a6d535</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr Consultant Network Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=979ce901773b1519</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Portless</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fac81252bedf828b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cost Engineer – Data Analytics</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69730719f6ab06e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sagenet</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1d9bc5af2a95ba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E-Payments Risk Data Scientist (Machine Learning)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, Git, Databricks, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=153070e1a4c17c69</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist, AI/ML – Visa Consulting and Analytics</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Copilot, Git, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a23f58a73f78740d</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (2-Year Temp Position with Potential for Permanent Hire)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Metropolitan Council of the Twin Cities</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=822af6f87b5a1291</t>
         </is>
       </c>
     </row>
